--- a/public/tally_templates/STANDARD.xlsx
+++ b/public/tally_templates/STANDARD.xlsx
@@ -23976,7 +23976,6 @@
       </c>
       <c r="H98" s="347">
         <f>H55</f>
-        <v>NaN</v>
       </c>
       <c r="I98" s="364" t="s">
         <v>114</v>

--- a/public/tally_templates/STANDARD.xlsx
+++ b/public/tally_templates/STANDARD.xlsx
@@ -1322,7 +1322,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="10">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3359,7 +3359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="585">
+  <cellXfs count="596">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5102,6 +5102,39 @@
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5110,11 +5143,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5382,7 +5415,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -6112,7 +6145,7 @@
       <c r="A6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="164" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -6180,7 +6213,7 @@
       <c r="A8" s="204" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="204" t="s">
+      <c r="B8" s="164" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="204"/>
@@ -6192,7 +6225,7 @@
         <v>61</v>
       </c>
       <c r="I8" s="189"/>
-      <c r="J8" s="189" t="s">
+      <c r="J8" s="164" t="s">
         <v>62</v>
       </c>
       <c r="K8" s="189"/>
@@ -6243,7 +6276,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="209" t="s">
         <v>11</v>
       </c>
@@ -6284,7 +6317,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="213"/>
       <c r="B11" s="213"/>
       <c r="C11" s="266"/>
@@ -7098,7 +7131,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -7394,7 +7427,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -7454,7 +7487,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="585" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -7463,14 +7496,14 @@
       <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="586"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="1"/>
       <c r="K4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="587"/>
       <c r="M4" s="14"/>
       <c r="N4" s="14"/>
       <c r="O4" s="14"/>
@@ -7516,21 +7549,21 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="586"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="586"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="588" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="18"/>
@@ -10157,7 +10190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
@@ -10819,7 +10852,7 @@
       </c>
       <c r="B6" s="260"/>
       <c r="C6" s="260"/>
-      <c r="D6" s="260" t="s">
+      <c r="D6" s="550" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="260"/>
@@ -10835,7 +10868,7 @@
       <c r="O6" s="260" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="40"/>
+      <c r="P6" s="594"/>
       <c r="Q6" s="40"/>
       <c r="R6" s="122" t="str">
         <f>'Final Work'!G4</f>
@@ -10907,7 +10940,7 @@
       <c r="A8" s="148" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="148"/>
+      <c r="B8" s="595"/>
       <c r="C8" s="148"/>
       <c r="D8" s="390" t="s">
         <v>62</v>
@@ -10925,7 +10958,7 @@
       <c r="O8" s="390" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="148"/>
+      <c r="P8" s="595"/>
       <c r="Q8" s="148"/>
       <c r="R8" s="389">
         <f>'Final Work'!G6</f>
@@ -10942,7 +10975,7 @@
       </c>
       <c r="Z8" s="389"/>
       <c r="AA8" s="389"/>
-      <c r="AB8" s="389" t="s">
+      <c r="AB8" s="595" t="s">
         <v>25</v>
       </c>
       <c r="AC8" s="389"/>
@@ -13778,7 +13811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -14572,7 +14605,7 @@
       <c r="A6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="164" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -14582,13 +14615,13 @@
       <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="189"/>
+      <c r="H6" s="164"/>
       <c r="I6" s="189"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="205"/>
+      <c r="L6" s="591"/>
       <c r="M6" s="189"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -14634,7 +14667,7 @@
       <c r="A8" s="204" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="592" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3"/>
@@ -14644,13 +14677,13 @@
       <c r="G8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="189"/>
+      <c r="H8" s="164"/>
       <c r="I8" s="189"/>
       <c r="J8" s="3"/>
       <c r="K8" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="189"/>
+      <c r="L8" s="164"/>
       <c r="M8" s="189"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -15735,7 +15768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="60"/>
     <pageSetUpPr fitToPage="1"/>
@@ -16465,7 +16498,7 @@
       <c r="A6" s="204" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="164" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -16533,7 +16566,7 @@
       <c r="A8" s="204" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="204" t="s">
+      <c r="B8" s="164" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="204"/>
@@ -16545,7 +16578,7 @@
         <v>61</v>
       </c>
       <c r="I8" s="189"/>
-      <c r="J8" s="189" t="s">
+      <c r="J8" s="164" t="s">
         <v>62</v>
       </c>
       <c r="K8" s="189"/>
@@ -16596,7 +16629,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="206" t="s">
         <v>11</v>
       </c>
@@ -16637,7 +16670,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="210"/>
       <c r="B11" s="210"/>
       <c r="C11" s="266"/>
@@ -17451,7 +17484,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y79"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -18128,7 +18161,7 @@
       <c r="F4" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="205"/>
+      <c r="G4" s="591"/>
       <c r="H4" s="189"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -18188,7 +18221,7 @@
       <c r="F6" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="298" t="s">
+      <c r="G6" s="593" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3"/>
@@ -19251,7 +19284,7 @@
       <c r="F43" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G43" s="298" t="s">
+      <c r="G43" s="593" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="3"/>
@@ -20350,7 +20383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -21162,7 +21195,7 @@
       <c r="G8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="189" t="s">
+      <c r="H8" s="164" t="s">
         <v>101</v>
       </c>
       <c r="I8" s="189"/>
@@ -22384,7 +22417,7 @@
       <c r="G51" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H51" s="189" t="s">
+      <c r="H51" s="164" t="s">
         <v>101</v>
       </c>
       <c r="I51" s="189"/>
@@ -22509,27 +22542,17 @@
       <c r="Y54" s="1"/>
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="362" t="s">
-        <v>111</v>
-      </c>
+      <c r="A55" s="362"/>
       <c r="B55" s="363"/>
-      <c r="C55" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C55" s="345"/>
       <c r="D55" s="53"/>
       <c r="E55" s="53"/>
-      <c r="F55" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G55" s="346">
-        <v>-17.2</v>
-      </c>
+      <c r="F55" s="346"/>
+      <c r="G55" s="346"/>
       <c r="H55" s="347" t="s">
         <v>113</v>
       </c>
-      <c r="I55" s="364" t="s">
-        <v>114</v>
-      </c>
+      <c r="I55" s="364"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -22548,27 +22571,15 @@
       <c r="Y55" s="1"/>
     </row>
     <row r="56" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="365" t="s">
-        <v>115</v>
-      </c>
+      <c r="A56" s="365"/>
       <c r="B56" s="366"/>
-      <c r="C56" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C56" s="349"/>
       <c r="D56" s="226"/>
       <c r="E56" s="226"/>
-      <c r="F56" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G56" s="350">
-        <v>-17.9</v>
-      </c>
-      <c r="H56" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I56" s="368" t="s">
-        <v>117</v>
-      </c>
+      <c r="F56" s="350"/>
+      <c r="G56" s="350"/>
+      <c r="H56" s="367"/>
+      <c r="I56" s="368"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -22587,27 +22598,15 @@
       <c r="Y56" s="1"/>
     </row>
     <row r="57" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="365" t="s">
-        <v>118</v>
-      </c>
+      <c r="A57" s="365"/>
       <c r="B57" s="366"/>
-      <c r="C57" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C57" s="349"/>
       <c r="D57" s="223"/>
       <c r="E57" s="168"/>
-      <c r="F57" s="350">
-        <v>3</v>
-      </c>
-      <c r="G57" s="350">
-        <v>3</v>
-      </c>
-      <c r="H57" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I57" s="368" t="s">
-        <v>117</v>
-      </c>
+      <c r="F57" s="350"/>
+      <c r="G57" s="350"/>
+      <c r="H57" s="367"/>
+      <c r="I57" s="368"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -22626,27 +22625,15 @@
       <c r="Y57" s="1"/>
     </row>
     <row r="58" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A58" s="365" t="s">
-        <v>119</v>
-      </c>
+      <c r="A58" s="365"/>
       <c r="B58" s="366"/>
-      <c r="C58" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C58" s="349"/>
       <c r="D58" s="223"/>
       <c r="E58" s="168"/>
-      <c r="F58" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G58" s="350">
-        <v>-18.2</v>
-      </c>
-      <c r="H58" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I58" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F58" s="350"/>
+      <c r="G58" s="350"/>
+      <c r="H58" s="367"/>
+      <c r="I58" s="368"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -22665,27 +22652,15 @@
       <c r="Y58" s="1"/>
     </row>
     <row r="59" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A59" s="369" t="s">
-        <v>120</v>
-      </c>
+      <c r="A59" s="369"/>
       <c r="B59" s="370"/>
-      <c r="C59" s="352" t="s">
-        <v>112</v>
-      </c>
+      <c r="C59" s="352"/>
       <c r="D59" s="371"/>
       <c r="E59" s="372"/>
-      <c r="F59" s="353">
-        <v>-18</v>
-      </c>
-      <c r="G59" s="353">
-        <v>-18.3</v>
-      </c>
-      <c r="H59" s="373" t="s">
-        <v>116</v>
-      </c>
-      <c r="I59" s="374" t="s">
-        <v>114</v>
-      </c>
+      <c r="F59" s="353"/>
+      <c r="G59" s="353"/>
+      <c r="H59" s="373"/>
+      <c r="I59" s="374"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -22704,27 +22679,15 @@
       <c r="Y59" s="1"/>
     </row>
     <row r="60" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="375" t="s">
-        <v>121</v>
-      </c>
+      <c r="A60" s="375"/>
       <c r="B60" s="363"/>
-      <c r="C60" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C60" s="345"/>
       <c r="D60" s="187"/>
       <c r="E60" s="56"/>
-      <c r="F60" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G60" s="346">
-        <v>-17.6</v>
-      </c>
-      <c r="H60" s="376" t="s">
-        <v>116</v>
-      </c>
-      <c r="I60" s="364" t="s">
-        <v>114</v>
-      </c>
+      <c r="F60" s="346"/>
+      <c r="G60" s="346"/>
+      <c r="H60" s="376"/>
+      <c r="I60" s="364"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -22743,27 +22706,15 @@
       <c r="Y60" s="1"/>
     </row>
     <row r="61" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A61" s="365" t="s">
-        <v>122</v>
-      </c>
+      <c r="A61" s="365"/>
       <c r="B61" s="349"/>
-      <c r="C61" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C61" s="349"/>
       <c r="D61" s="223"/>
       <c r="E61" s="168"/>
-      <c r="F61" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G61" s="350">
-        <v>-17.9</v>
-      </c>
-      <c r="H61" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I61" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F61" s="350"/>
+      <c r="G61" s="350"/>
+      <c r="H61" s="367"/>
+      <c r="I61" s="368"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -22782,27 +22733,15 @@
       <c r="Y61" s="1"/>
     </row>
     <row r="62" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A62" s="365" t="s">
-        <v>123</v>
-      </c>
+      <c r="A62" s="365"/>
       <c r="B62" s="349"/>
-      <c r="C62" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C62" s="349"/>
       <c r="D62" s="223"/>
       <c r="E62" s="168"/>
-      <c r="F62" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G62" s="350">
-        <v>-18.6</v>
-      </c>
-      <c r="H62" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I62" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F62" s="350"/>
+      <c r="G62" s="350"/>
+      <c r="H62" s="367"/>
+      <c r="I62" s="368"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -22821,27 +22760,15 @@
       <c r="Y62" s="1"/>
     </row>
     <row r="63" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A63" s="365" t="s">
-        <v>124</v>
-      </c>
+      <c r="A63" s="365"/>
       <c r="B63" s="349"/>
-      <c r="C63" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C63" s="349"/>
       <c r="D63" s="223"/>
       <c r="E63" s="168"/>
-      <c r="F63" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G63" s="350">
-        <v>-18</v>
-      </c>
-      <c r="H63" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I63" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F63" s="350"/>
+      <c r="G63" s="350"/>
+      <c r="H63" s="367"/>
+      <c r="I63" s="368"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -22860,27 +22787,15 @@
       <c r="Y63" s="1"/>
     </row>
     <row r="64" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="377" t="s">
-        <v>125</v>
-      </c>
+      <c r="A64" s="377"/>
       <c r="B64" s="352"/>
-      <c r="C64" s="352" t="s">
-        <v>112</v>
-      </c>
+      <c r="C64" s="352"/>
       <c r="D64" s="371"/>
       <c r="E64" s="372"/>
-      <c r="F64" s="353">
-        <v>-18</v>
-      </c>
-      <c r="G64" s="378">
-        <v>-18.4</v>
-      </c>
-      <c r="H64" s="373" t="s">
-        <v>116</v>
-      </c>
-      <c r="I64" s="374" t="s">
-        <v>114</v>
-      </c>
+      <c r="F64" s="353"/>
+      <c r="G64" s="378"/>
+      <c r="H64" s="373"/>
+      <c r="I64" s="374"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -22899,27 +22814,15 @@
       <c r="Y64" s="1"/>
     </row>
     <row r="65" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="362" t="s">
-        <v>126</v>
-      </c>
+      <c r="A65" s="362"/>
       <c r="B65" s="345"/>
-      <c r="C65" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C65" s="345"/>
       <c r="D65" s="187"/>
       <c r="E65" s="56"/>
-      <c r="F65" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G65" s="379">
-        <v>-18.4</v>
-      </c>
-      <c r="H65" s="376" t="s">
-        <v>116</v>
-      </c>
-      <c r="I65" s="364" t="s">
-        <v>114</v>
-      </c>
+      <c r="F65" s="346"/>
+      <c r="G65" s="379"/>
+      <c r="H65" s="376"/>
+      <c r="I65" s="364"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -22938,27 +22841,15 @@
       <c r="Y65" s="1"/>
     </row>
     <row r="66" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="380" t="s">
-        <v>127</v>
-      </c>
+      <c r="A66" s="380"/>
       <c r="B66" s="349"/>
-      <c r="C66" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C66" s="349"/>
       <c r="D66" s="223"/>
       <c r="E66" s="168"/>
-      <c r="F66" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G66" s="381">
-        <v>-18.2</v>
-      </c>
-      <c r="H66" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I66" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F66" s="350"/>
+      <c r="G66" s="381"/>
+      <c r="H66" s="367"/>
+      <c r="I66" s="368"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -22977,27 +22868,15 @@
       <c r="Y66" s="1"/>
     </row>
     <row r="67" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A67" s="380" t="s">
-        <v>128</v>
-      </c>
+      <c r="A67" s="380"/>
       <c r="B67" s="349"/>
-      <c r="C67" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C67" s="349"/>
       <c r="D67" s="223"/>
       <c r="E67" s="168"/>
-      <c r="F67" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G67" s="381">
-        <v>-18.1</v>
-      </c>
-      <c r="H67" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I67" s="368" t="s">
-        <v>117</v>
-      </c>
+      <c r="F67" s="350"/>
+      <c r="G67" s="381"/>
+      <c r="H67" s="367"/>
+      <c r="I67" s="368"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -23016,27 +22895,15 @@
       <c r="Y67" s="1"/>
     </row>
     <row r="68" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A68" s="349" t="s">
-        <v>129</v>
-      </c>
+      <c r="A68" s="349"/>
       <c r="B68" s="349"/>
-      <c r="C68" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C68" s="349"/>
       <c r="D68" s="223"/>
       <c r="E68" s="168"/>
-      <c r="F68" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G68" s="381">
-        <v>-18.2</v>
-      </c>
-      <c r="H68" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I68" s="349" t="s">
-        <v>117</v>
-      </c>
+      <c r="F68" s="350"/>
+      <c r="G68" s="381"/>
+      <c r="H68" s="367"/>
+      <c r="I68" s="349"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -23055,27 +22922,15 @@
       <c r="Y68" s="1"/>
     </row>
     <row r="69" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A69" s="382" t="s">
-        <v>130</v>
-      </c>
+      <c r="A69" s="382"/>
       <c r="B69" s="382"/>
-      <c r="C69" s="352" t="s">
-        <v>112</v>
-      </c>
+      <c r="C69" s="352"/>
       <c r="D69" s="371"/>
       <c r="E69" s="372"/>
-      <c r="F69" s="353">
-        <v>-18</v>
-      </c>
-      <c r="G69" s="383">
-        <v>-18.1</v>
-      </c>
-      <c r="H69" s="373" t="s">
-        <v>116</v>
-      </c>
-      <c r="I69" s="382" t="s">
-        <v>117</v>
-      </c>
+      <c r="F69" s="353"/>
+      <c r="G69" s="383"/>
+      <c r="H69" s="373"/>
+      <c r="I69" s="382"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -23094,27 +22949,15 @@
       <c r="Y69" s="1"/>
     </row>
     <row r="70" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="384" t="s">
-        <v>131</v>
-      </c>
+      <c r="A70" s="384"/>
       <c r="B70" s="384"/>
-      <c r="C70" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C70" s="345"/>
       <c r="D70" s="29"/>
       <c r="E70" s="27"/>
-      <c r="F70" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G70" s="385">
-        <v>-18</v>
-      </c>
-      <c r="H70" s="376" t="s">
-        <v>116</v>
-      </c>
-      <c r="I70" s="384" t="s">
-        <v>117</v>
-      </c>
+      <c r="F70" s="346"/>
+      <c r="G70" s="385"/>
+      <c r="H70" s="376"/>
+      <c r="I70" s="384"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -23133,27 +22976,15 @@
       <c r="Y70" s="1"/>
     </row>
     <row r="71" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A71" s="349" t="s">
-        <v>132</v>
-      </c>
+      <c r="A71" s="349"/>
       <c r="B71" s="349"/>
-      <c r="C71" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C71" s="349"/>
       <c r="D71" s="223"/>
       <c r="E71" s="168"/>
-      <c r="F71" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G71" s="381">
-        <v>-17.9</v>
-      </c>
-      <c r="H71" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I71" s="349" t="s">
-        <v>117</v>
-      </c>
+      <c r="F71" s="350"/>
+      <c r="G71" s="381"/>
+      <c r="H71" s="367"/>
+      <c r="I71" s="349"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -23172,27 +23003,15 @@
       <c r="Y71" s="1"/>
     </row>
     <row r="72" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A72" s="312" t="s">
-        <v>133</v>
-      </c>
+      <c r="A72" s="312"/>
       <c r="B72" s="312"/>
-      <c r="C72" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C72" s="349"/>
       <c r="D72" s="223"/>
       <c r="E72" s="168"/>
-      <c r="F72" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G72" s="386">
-        <v>-18.3</v>
-      </c>
-      <c r="H72" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I72" s="226" t="s">
-        <v>117</v>
-      </c>
+      <c r="F72" s="350"/>
+      <c r="G72" s="386"/>
+      <c r="H72" s="367"/>
+      <c r="I72" s="226"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -23834,7 +23653,7 @@
       <c r="G94" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H94" s="189" t="s">
+      <c r="H94" s="164" t="s">
         <v>101</v>
       </c>
       <c r="I94" s="189"/>
@@ -23959,27 +23778,17 @@
       <c r="Y97" s="1"/>
     </row>
     <row r="98" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A98" s="362" t="s">
-        <v>141</v>
-      </c>
+      <c r="A98" s="362"/>
       <c r="B98" s="363"/>
-      <c r="C98" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C98" s="345"/>
       <c r="D98" s="53"/>
       <c r="E98" s="53"/>
-      <c r="F98" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G98" s="346">
-        <v>-17.3</v>
-      </c>
+      <c r="F98" s="346"/>
+      <c r="G98" s="346"/>
       <c r="H98" s="347">
         <f>H55</f>
       </c>
-      <c r="I98" s="364" t="s">
-        <v>114</v>
-      </c>
+      <c r="I98" s="364"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -23998,27 +23807,15 @@
       <c r="Y98" s="1"/>
     </row>
     <row r="99" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A99" s="365" t="s">
-        <v>142</v>
-      </c>
+      <c r="A99" s="365"/>
       <c r="B99" s="366"/>
-      <c r="C99" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C99" s="349"/>
       <c r="D99" s="226"/>
       <c r="E99" s="226"/>
-      <c r="F99" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G99" s="350">
-        <v>-17.4</v>
-      </c>
-      <c r="H99" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I99" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F99" s="350"/>
+      <c r="G99" s="350"/>
+      <c r="H99" s="367"/>
+      <c r="I99" s="368"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -24037,27 +23834,15 @@
       <c r="Y99" s="1"/>
     </row>
     <row r="100" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A100" s="365" t="s">
-        <v>143</v>
-      </c>
+      <c r="A100" s="365"/>
       <c r="B100" s="366"/>
-      <c r="C100" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C100" s="349"/>
       <c r="D100" s="223"/>
       <c r="E100" s="168"/>
-      <c r="F100" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G100" s="350">
-        <v>-18.1</v>
-      </c>
-      <c r="H100" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I100" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F100" s="350"/>
+      <c r="G100" s="350"/>
+      <c r="H100" s="367"/>
+      <c r="I100" s="368"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -24076,27 +23861,15 @@
       <c r="Y100" s="1"/>
     </row>
     <row r="101" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A101" s="365" t="s">
-        <v>144</v>
-      </c>
+      <c r="A101" s="365"/>
       <c r="B101" s="366"/>
-      <c r="C101" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C101" s="349"/>
       <c r="D101" s="223"/>
       <c r="E101" s="168"/>
-      <c r="F101" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G101" s="350">
-        <v>-16.5</v>
-      </c>
-      <c r="H101" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I101" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F101" s="350"/>
+      <c r="G101" s="350"/>
+      <c r="H101" s="367"/>
+      <c r="I101" s="368"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -24115,27 +23888,15 @@
       <c r="Y101" s="1"/>
     </row>
     <row r="102" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A102" s="369" t="s">
-        <v>145</v>
-      </c>
+      <c r="A102" s="369"/>
       <c r="B102" s="370"/>
-      <c r="C102" s="352" t="s">
-        <v>112</v>
-      </c>
+      <c r="C102" s="352"/>
       <c r="D102" s="371"/>
       <c r="E102" s="372"/>
-      <c r="F102" s="353">
-        <v>-18</v>
-      </c>
-      <c r="G102" s="353">
-        <v>-17</v>
-      </c>
-      <c r="H102" s="373" t="s">
-        <v>116</v>
-      </c>
-      <c r="I102" s="374" t="s">
-        <v>114</v>
-      </c>
+      <c r="F102" s="353"/>
+      <c r="G102" s="353"/>
+      <c r="H102" s="373"/>
+      <c r="I102" s="374"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -24154,27 +23915,15 @@
       <c r="Y102" s="1"/>
     </row>
     <row r="103" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A103" s="375" t="s">
-        <v>146</v>
-      </c>
+      <c r="A103" s="375"/>
       <c r="B103" s="363"/>
-      <c r="C103" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C103" s="345"/>
       <c r="D103" s="187"/>
       <c r="E103" s="56"/>
-      <c r="F103" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G103" s="346">
-        <v>-17.9</v>
-      </c>
-      <c r="H103" s="376" t="s">
-        <v>116</v>
-      </c>
-      <c r="I103" s="364" t="s">
-        <v>114</v>
-      </c>
+      <c r="F103" s="346"/>
+      <c r="G103" s="346"/>
+      <c r="H103" s="376"/>
+      <c r="I103" s="364"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -24193,27 +23942,15 @@
       <c r="Y103" s="1"/>
     </row>
     <row r="104" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A104" s="365" t="s">
-        <v>147</v>
-      </c>
+      <c r="A104" s="365"/>
       <c r="B104" s="349"/>
-      <c r="C104" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C104" s="349"/>
       <c r="D104" s="223"/>
       <c r="E104" s="168"/>
-      <c r="F104" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G104" s="350">
-        <v>-18</v>
-      </c>
-      <c r="H104" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I104" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F104" s="350"/>
+      <c r="G104" s="350"/>
+      <c r="H104" s="367"/>
+      <c r="I104" s="368"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -24232,27 +23969,15 @@
       <c r="Y104" s="1"/>
     </row>
     <row r="105" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A105" s="365" t="s">
-        <v>148</v>
-      </c>
+      <c r="A105" s="365"/>
       <c r="B105" s="349"/>
-      <c r="C105" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C105" s="349"/>
       <c r="D105" s="223"/>
       <c r="E105" s="168"/>
-      <c r="F105" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G105" s="350">
-        <v>-16.7</v>
-      </c>
-      <c r="H105" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I105" s="368" t="s">
-        <v>114</v>
-      </c>
+      <c r="F105" s="350"/>
+      <c r="G105" s="350"/>
+      <c r="H105" s="367"/>
+      <c r="I105" s="368"/>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -24271,27 +23996,15 @@
       <c r="Y105" s="1"/>
     </row>
     <row r="106" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A106" s="365" t="s">
-        <v>149</v>
-      </c>
+      <c r="A106" s="365"/>
       <c r="B106" s="349"/>
-      <c r="C106" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C106" s="349"/>
       <c r="D106" s="223"/>
       <c r="E106" s="168"/>
-      <c r="F106" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G106" s="350">
-        <v>-18.1</v>
-      </c>
-      <c r="H106" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I106" s="368" t="s">
-        <v>117</v>
-      </c>
+      <c r="F106" s="350"/>
+      <c r="G106" s="350"/>
+      <c r="H106" s="367"/>
+      <c r="I106" s="368"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -24310,27 +24023,15 @@
       <c r="Y106" s="1"/>
     </row>
     <row r="107" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A107" s="377" t="s">
-        <v>150</v>
-      </c>
+      <c r="A107" s="377"/>
       <c r="B107" s="352"/>
-      <c r="C107" s="352" t="s">
-        <v>112</v>
-      </c>
+      <c r="C107" s="352"/>
       <c r="D107" s="371"/>
       <c r="E107" s="372"/>
-      <c r="F107" s="353">
-        <v>-18</v>
-      </c>
-      <c r="G107" s="378">
-        <v>-17.5</v>
-      </c>
-      <c r="H107" s="373" t="s">
-        <v>116</v>
-      </c>
-      <c r="I107" s="374" t="s">
-        <v>117</v>
-      </c>
+      <c r="F107" s="353"/>
+      <c r="G107" s="378"/>
+      <c r="H107" s="373"/>
+      <c r="I107" s="374"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -24349,27 +24050,15 @@
       <c r="Y107" s="1"/>
     </row>
     <row r="108" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A108" s="362" t="s">
-        <v>151</v>
-      </c>
+      <c r="A108" s="362"/>
       <c r="B108" s="345"/>
-      <c r="C108" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C108" s="345"/>
       <c r="D108" s="187"/>
       <c r="E108" s="56"/>
-      <c r="F108" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G108" s="379">
-        <v>-17.7</v>
-      </c>
-      <c r="H108" s="376" t="s">
-        <v>116</v>
-      </c>
-      <c r="I108" s="364" t="s">
-        <v>117</v>
-      </c>
+      <c r="F108" s="346"/>
+      <c r="G108" s="379"/>
+      <c r="H108" s="376"/>
+      <c r="I108" s="364"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -24388,27 +24077,15 @@
       <c r="Y108" s="1"/>
     </row>
     <row r="109" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A109" s="380" t="s">
-        <v>152</v>
-      </c>
+      <c r="A109" s="380"/>
       <c r="B109" s="349"/>
-      <c r="C109" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C109" s="349"/>
       <c r="D109" s="223"/>
       <c r="E109" s="168"/>
-      <c r="F109" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G109" s="381">
-        <v>-17</v>
-      </c>
-      <c r="H109" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I109" s="368" t="s">
-        <v>117</v>
-      </c>
+      <c r="F109" s="350"/>
+      <c r="G109" s="381"/>
+      <c r="H109" s="367"/>
+      <c r="I109" s="368"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -24427,27 +24104,15 @@
       <c r="Y109" s="1"/>
     </row>
     <row r="110" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A110" s="380" t="s">
-        <v>153</v>
-      </c>
+      <c r="A110" s="380"/>
       <c r="B110" s="349"/>
-      <c r="C110" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C110" s="349"/>
       <c r="D110" s="223"/>
       <c r="E110" s="168"/>
-      <c r="F110" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G110" s="381">
-        <v>-16.9</v>
-      </c>
-      <c r="H110" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I110" s="368" t="s">
-        <v>117</v>
-      </c>
+      <c r="F110" s="350"/>
+      <c r="G110" s="381"/>
+      <c r="H110" s="367"/>
+      <c r="I110" s="368"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -24466,27 +24131,15 @@
       <c r="Y110" s="1"/>
     </row>
     <row r="111" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A111" s="349" t="s">
-        <v>154</v>
-      </c>
+      <c r="A111" s="349"/>
       <c r="B111" s="349"/>
-      <c r="C111" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C111" s="349"/>
       <c r="D111" s="223"/>
       <c r="E111" s="168"/>
-      <c r="F111" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G111" s="381">
-        <v>-17.5</v>
-      </c>
-      <c r="H111" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I111" s="349" t="s">
-        <v>117</v>
-      </c>
+      <c r="F111" s="350"/>
+      <c r="G111" s="381"/>
+      <c r="H111" s="367"/>
+      <c r="I111" s="349"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -24505,27 +24158,15 @@
       <c r="Y111" s="1"/>
     </row>
     <row r="112" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A112" s="382" t="s">
-        <v>155</v>
-      </c>
+      <c r="A112" s="382"/>
       <c r="B112" s="382"/>
-      <c r="C112" s="352" t="s">
-        <v>112</v>
-      </c>
+      <c r="C112" s="352"/>
       <c r="D112" s="371"/>
       <c r="E112" s="372"/>
-      <c r="F112" s="353">
-        <v>-18</v>
-      </c>
-      <c r="G112" s="383">
-        <v>-18</v>
-      </c>
-      <c r="H112" s="373" t="s">
-        <v>116</v>
-      </c>
-      <c r="I112" s="382" t="s">
-        <v>117</v>
-      </c>
+      <c r="F112" s="353"/>
+      <c r="G112" s="383"/>
+      <c r="H112" s="373"/>
+      <c r="I112" s="382"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
@@ -24544,27 +24185,15 @@
       <c r="Y112" s="1"/>
     </row>
     <row r="113" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A113" s="384" t="s">
-        <v>156</v>
-      </c>
+      <c r="A113" s="384"/>
       <c r="B113" s="384"/>
-      <c r="C113" s="345" t="s">
-        <v>112</v>
-      </c>
+      <c r="C113" s="345"/>
       <c r="D113" s="29"/>
       <c r="E113" s="27"/>
-      <c r="F113" s="346">
-        <v>-18</v>
-      </c>
-      <c r="G113" s="385">
-        <v>-17.8</v>
-      </c>
-      <c r="H113" s="376" t="s">
-        <v>116</v>
-      </c>
-      <c r="I113" s="384" t="s">
-        <v>117</v>
-      </c>
+      <c r="F113" s="346"/>
+      <c r="G113" s="385"/>
+      <c r="H113" s="376"/>
+      <c r="I113" s="384"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -24583,27 +24212,15 @@
       <c r="Y113" s="1"/>
     </row>
     <row r="114" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A114" s="349" t="s">
-        <v>157</v>
-      </c>
+      <c r="A114" s="349"/>
       <c r="B114" s="349"/>
-      <c r="C114" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C114" s="349"/>
       <c r="D114" s="223"/>
       <c r="E114" s="168"/>
-      <c r="F114" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G114" s="381">
-        <v>-17.6</v>
-      </c>
-      <c r="H114" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I114" s="349" t="s">
-        <v>117</v>
-      </c>
+      <c r="F114" s="350"/>
+      <c r="G114" s="381"/>
+      <c r="H114" s="367"/>
+      <c r="I114" s="349"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
@@ -24622,27 +24239,15 @@
       <c r="Y114" s="1"/>
     </row>
     <row r="115" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A115" s="312" t="s">
-        <v>158</v>
-      </c>
+      <c r="A115" s="312"/>
       <c r="B115" s="312"/>
-      <c r="C115" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C115" s="349"/>
       <c r="D115" s="223"/>
       <c r="E115" s="168"/>
-      <c r="F115" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G115" s="386">
-        <v>-17.5</v>
-      </c>
-      <c r="H115" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I115" s="226" t="s">
-        <v>117</v>
-      </c>
+      <c r="F115" s="350"/>
+      <c r="G115" s="386"/>
+      <c r="H115" s="367"/>
+      <c r="I115" s="226"/>
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
@@ -24661,27 +24266,15 @@
       <c r="Y115" s="1"/>
     </row>
     <row r="116" ht="20.1" customHeight="1" hidden="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A116" s="312" t="s">
-        <v>159</v>
-      </c>
+      <c r="A116" s="312"/>
       <c r="B116" s="312"/>
-      <c r="C116" s="349" t="s">
-        <v>112</v>
-      </c>
+      <c r="C116" s="349"/>
       <c r="D116" s="223"/>
       <c r="E116" s="168"/>
-      <c r="F116" s="350">
-        <v>-18</v>
-      </c>
-      <c r="G116" s="386">
-        <v>-16.9</v>
-      </c>
-      <c r="H116" s="367" t="s">
-        <v>116</v>
-      </c>
-      <c r="I116" s="226" t="s">
-        <v>117</v>
-      </c>
+      <c r="F116" s="350"/>
+      <c r="G116" s="386"/>
+      <c r="H116" s="367"/>
+      <c r="I116" s="226"/>
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
       <c r="L116" s="1"/>
@@ -25253,7 +24846,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y51"/>
   <sheetFormatPr defaultRowHeight="17.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -25917,11 +25510,11 @@
       <c r="A6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="152"/>
+      <c r="B6" s="589"/>
       <c r="C6" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="14"/>
+      <c r="D6" s="590"/>
       <c r="E6" s="14"/>
       <c r="F6" s="9"/>
       <c r="G6" s="154" t="s">
@@ -25980,17 +25573,17 @@
       <c r="A8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="156"/>
+      <c r="B8" s="590"/>
       <c r="C8" s="153" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="14"/>
+      <c r="D8" s="590"/>
       <c r="E8" s="14"/>
       <c r="F8" s="153"/>
       <c r="G8" s="157" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="18"/>
+      <c r="H8" s="588"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -29084,7 +28677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor indexed="59"/>
     <pageSetUpPr fitToPage="1"/>
@@ -29878,7 +29471,7 @@
       <c r="A6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="164" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -29888,13 +29481,13 @@
       <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="189"/>
+      <c r="H6" s="164"/>
       <c r="I6" s="189"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="205"/>
+      <c r="L6" s="591"/>
       <c r="M6" s="189"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -29940,7 +29533,7 @@
       <c r="A8" s="204" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="592" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="274"/>
@@ -29950,13 +29543,13 @@
       <c r="G8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="189"/>
+      <c r="H8" s="164"/>
       <c r="I8" s="189"/>
       <c r="J8" s="3"/>
       <c r="K8" s="204" t="s">
         <v>40</v>
       </c>
-      <c r="L8" s="189"/>
+      <c r="L8" s="164"/>
       <c r="M8" s="189"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
